--- a/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort2.xlsx
+++ b/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure 3\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AAAFC3-C8DC-4102-91BB-F0B11551F3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE44A09-EE3B-4E90-886C-858EE95CAB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2197215B-64E2-46CD-9E46-6556A9BFA39E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="39">
   <si>
     <t>Mice</t>
   </si>
@@ -560,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BC7C5F-046B-4F9E-B94E-ABDDA46AE673}">
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -3099,6 +3099,146 @@
       </c>
       <c r="D181" s="1">
         <v>33.299999999999997</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C182" s="2">
+        <v>45586</v>
+      </c>
+      <c r="D182">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C183" s="2">
+        <v>45586</v>
+      </c>
+      <c r="D183">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C184" s="2">
+        <v>45586</v>
+      </c>
+      <c r="D184">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C185" s="2">
+        <v>45586</v>
+      </c>
+      <c r="D185">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C186" s="2">
+        <v>45586</v>
+      </c>
+      <c r="D186">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C187" s="2">
+        <v>45538</v>
+      </c>
+      <c r="D187">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C188" s="2">
+        <v>45538</v>
+      </c>
+      <c r="D188">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C189" s="2">
+        <v>45538</v>
+      </c>
+      <c r="D189">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C190" s="2">
+        <v>45538</v>
+      </c>
+      <c r="D190">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C191" s="2">
+        <v>45538</v>
+      </c>
+      <c r="D191">
+        <v>28.2</v>
       </c>
     </row>
   </sheetData>
@@ -6158,11 +6298,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6387,27 +6528,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F7B0A92-6AE3-4754-A87C-9BC386EADEAF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FA683CE-1C66-495C-B415-AE7EB6D3803A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="b159d527-15c9-467a-b762-1e479e1f7549"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6432,9 +6563,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FA683CE-1C66-495C-B415-AE7EB6D3803A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F7B0A92-6AE3-4754-A87C-9BC386EADEAF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="b159d527-15c9-467a-b762-1e479e1f7549"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>